--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T03:12:48+00:00</t>
+    <t>2026-03-18T09:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -867,7 +867,7 @@
     <t>Patient.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address|Address}
+    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address}
 </t>
   </si>
   <si>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:24:52+00:00</t>
+    <t>2026-03-25T02:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T02:48:03+00:00</t>
+    <t>2026-03-25T03:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:05:28+00:00</t>
+    <t>2026-03-25T03:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:10:05+00:00</t>
+    <t>2026-03-25T03:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:26:10+00:00</t>
+    <t>2026-03-25T03:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$90</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="506">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:54:03+00:00</t>
+    <t>2026-04-01T03:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -920,6 +920,206 @@
     <t>PID-16</t>
   </si>
   <si>
+    <t>Patient.maritalStatus.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.coding.id</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.coding.extension</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Patient.multipleBirth[x]</t>
   </si>
   <si>
@@ -1002,29 +1202,7 @@
     <t>Patient.contact.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Patient.contact.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Patient.contact.modifierExtension</t>
@@ -1065,6 +1243,39 @@
     <t>NK1-7, NK1-3</t>
   </si>
   <si>
+    <t>Patient.contact.relationship.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.system</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.version</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.code</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.display</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.text</t>
+  </si>
+  <si>
     <t>Patient.contact.name</t>
   </si>
   <si>
@@ -1219,6 +1430,39 @@
   </si>
   <si>
     <t>PID-15, LAN-2</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.id</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.extension</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.coding</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.coding.id</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.coding.extension</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.coding.system</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.coding.version</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.coding.code</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.coding.display</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.text</t>
   </si>
   <si>
     <t>Patient.communication.preferred</t>
@@ -1668,11 +1912,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO57"/>
+  <dimension ref="A1:AO90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.83984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.40625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.40625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.91015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1699,7 +1943,7 @@
     <col min="26" max="26" width="46.8203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="27.49609375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1709,7 +1953,7 @@
     <col min="37" max="37" width="134.453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="34.98828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="33.76171875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="34.35546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -5130,7 +5374,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>278</v>
       </c>
@@ -5149,7 +5393,7 @@
         <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>81</v>
@@ -5281,12 +5525,8 @@
       <c r="M31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5334,7 +5574,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5346,19 +5586,19 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>293</v>
+        <v>220</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5366,14 +5606,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5392,20 +5632,18 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>296</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5441,19 +5679,19 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5465,30 +5703,30 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>301</v>
+        <v>220</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5502,28 +5740,28 @@
         <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5584,19 +5822,19 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>309</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -5604,10 +5842,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5630,13 +5868,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5687,7 +5925,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5719,10 +5957,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5748,10 +5986,10 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>192</v>
@@ -5792,19 +6030,19 @@
         <v>81</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5836,45 +6074,45 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>193</v>
+        <v>312</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5923,22 +6161,22 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>132</v>
+        <v>314</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
@@ -5947,7 +6185,7 @@
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -5955,10 +6193,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5969,7 +6207,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -5978,21 +6216,21 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6016,11 +6254,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6038,13 +6278,13 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
@@ -6053,27 +6293,27 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6087,26 +6327,26 @@
         <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>223</v>
+        <v>109</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6155,7 +6395,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6170,16 +6410,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>228</v>
+        <v>328</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6187,10 +6427,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6201,7 +6441,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6210,22 +6450,20 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>236</v>
+        <v>333</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6274,13 +6512,13 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
@@ -6289,27 +6527,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>237</v>
+        <v>335</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6323,26 +6561,28 @@
         <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K40" t="s" s="2">
-        <v>270</v>
+        <v>213</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6406,16 +6646,16 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -6423,10 +6663,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6446,20 +6686,22 @@
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6484,13 +6726,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6508,7 +6750,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6523,16 +6765,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>248</v>
+        <v>351</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6540,10 +6782,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6566,17 +6808,19 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6625,7 +6869,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6634,13 +6878,13 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>220</v>
@@ -6649,7 +6893,7 @@
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -6657,10 +6901,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6671,7 +6915,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -6683,16 +6927,20 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6740,13 +6988,13 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
@@ -6755,7 +7003,7 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>220</v>
@@ -6764,7 +7012,7 @@
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>81</v>
+        <v>368</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -6772,10 +7020,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6798,19 +7046,19 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>304</v>
+        <v>370</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6859,7 +7107,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6871,13 +7119,13 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>375</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>371</v>
+        <v>220</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
@@ -6891,10 +7139,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6917,13 +7165,13 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6974,7 +7222,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7006,10 +7254,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7035,10 +7283,10 @@
         <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>192</v>
@@ -7091,7 +7339,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7123,14 +7371,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>321</v>
+        <v>380</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7152,10 +7400,10 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>192</v>
@@ -7210,7 +7458,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7240,12 +7488,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7253,13 +7501,13 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>81</v>
@@ -7271,16 +7519,14 @@
         <v>279</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7305,13 +7551,11 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>115</v>
+        <v>388</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7329,13 +7573,13 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
@@ -7344,16 +7588,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>381</v>
+        <v>220</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7361,10 +7605,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7387,20 +7631,16 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>213</v>
+        <v>288</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7448,7 +7688,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>291</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7460,19 +7700,19 @@
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>388</v>
+        <v>220</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -7480,14 +7720,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>392</v>
+        <v>189</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7506,16 +7746,16 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>393</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>394</v>
+        <v>293</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>395</v>
+        <v>294</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>396</v>
+        <v>192</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7553,19 +7793,19 @@
         <v>81</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>296</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7577,30 +7817,30 @@
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>397</v>
+        <v>220</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>398</v>
+        <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7611,10 +7851,10 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>81</v>
@@ -7623,19 +7863,19 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>400</v>
+        <v>299</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
+        <v>300</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>402</v>
+        <v>301</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>403</v>
+        <v>302</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -7684,13 +7924,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>303</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -7699,16 +7939,16 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>358</v>
+        <v>304</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>404</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -7716,10 +7956,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7730,32 +7970,28 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>406</v>
+        <v>289</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -7803,25 +8039,25 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>405</v>
+        <v>291</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>410</v>
+        <v>220</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7835,21 +8071,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -7861,15 +8097,17 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>312</v>
+        <v>134</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -7906,31 +8144,31 @@
         <v>81</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>220</v>
@@ -7950,21 +8188,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -7973,21 +8211,23 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8035,22 +8275,22 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>220</v>
+        <v>314</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
@@ -8059,7 +8299,7 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8067,46 +8307,44 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>288</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8154,22 +8392,22 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>132</v>
+        <v>321</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
@@ -8178,18 +8416,18 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8197,13 +8435,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>81</v>
@@ -8212,18 +8450,18 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>415</v>
+        <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>416</v>
+        <v>324</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8271,10 +8509,10 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>414</v>
+        <v>327</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>89</v>
@@ -8286,16 +8524,16 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>202</v>
+        <v>328</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>419</v>
+        <v>329</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8303,10 +8541,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8314,7 +8552,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
@@ -8329,16 +8567,18 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>421</v>
+        <v>331</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>422</v>
+        <v>332</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -8362,13 +8602,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8386,10 +8626,10 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>420</v>
+        <v>334</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>89</v>
@@ -8401,23 +8641,3900 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="M64" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO57" t="s" s="2">
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO57">
+  <autoFilter ref="A1:AO90">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8427,7 +12544,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI89">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="453">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -979,123 +979,6 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Patient.maritalStatus.coding.id</t>
-  </si>
-  <si>
-    <t>Patient.maritalStatus.coding.extension</t>
-  </si>
-  <si>
-    <t>Patient.maritalStatus.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Patient.maritalStatus.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Patient.maritalStatus.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Patient.maritalStatus.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Patient.maritalStatus.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
     <t>Patient.maritalStatus.text</t>
   </si>
   <si>
@@ -1252,27 +1135,6 @@
     <t>Patient.contact.relationship.coding</t>
   </si>
   <si>
-    <t>Patient.contact.relationship.coding.id</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.extension</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.system</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.version</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.code</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.display</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.userSelected</t>
-  </si>
-  <si>
     <t>Patient.contact.relationship.text</t>
   </si>
   <si>
@@ -1439,27 +1301,6 @@
   </si>
   <si>
     <t>Patient.communication.language.coding</t>
-  </si>
-  <si>
-    <t>Patient.communication.language.coding.id</t>
-  </si>
-  <si>
-    <t>Patient.communication.language.coding.extension</t>
-  </si>
-  <si>
-    <t>Patient.communication.language.coding.system</t>
-  </si>
-  <si>
-    <t>Patient.communication.language.coding.version</t>
-  </si>
-  <si>
-    <t>Patient.communication.language.coding.code</t>
-  </si>
-  <si>
-    <t>Patient.communication.language.coding.display</t>
-  </si>
-  <si>
-    <t>Patient.communication.language.coding.userSelected</t>
   </si>
   <si>
     <t>Patient.communication.language.text</t>
@@ -1912,11 +1753,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO90"/>
+  <dimension ref="A1:AO69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.40625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.40625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.1015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.1015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.91015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -5840,7 +5681,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>306</v>
       </c>
@@ -5859,25 +5700,29 @@
         <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>288</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -5925,7 +5770,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5937,10 +5782,10 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -5949,7 +5794,7 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -5957,21 +5802,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -5983,18 +5828,20 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>315</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6030,43 +5877,43 @@
         <v>81</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>81</v>
+        <v>321</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6074,10 +5921,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6088,7 +5935,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6097,22 +5944,22 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>323</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6161,13 +6008,13 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
@@ -6176,16 +6023,16 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6193,10 +6040,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6207,7 +6054,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6216,21 +6063,23 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6278,42 +6127,42 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>336</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>322</v>
+        <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6327,27 +6176,25 @@
         <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>289</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>326</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6395,7 +6242,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6407,10 +6254,10 @@
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>328</v>
+        <v>220</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -6419,7 +6266,7 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6427,21 +6274,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6450,21 +6297,21 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>288</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>331</v>
+        <v>293</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6512,22 +6359,22 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>335</v>
+        <v>220</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>81</v>
@@ -6536,7 +6383,7 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6544,45 +6391,45 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>340</v>
+        <v>192</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>341</v>
+        <v>193</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6631,22 +6478,22 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>343</v>
+        <v>132</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -6655,13 +6502,13 @@
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>345</v>
       </c>
@@ -6677,19 +6524,19 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>346</v>
@@ -6697,11 +6544,9 @@
       <c r="M41" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6726,13 +6571,11 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6750,13 +6593,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6765,16 +6608,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6782,10 +6625,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6808,20 +6651,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6869,7 +6708,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>353</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6881,19 +6720,19 @@
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>359</v>
+        <v>220</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>360</v>
+        <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -6901,14 +6740,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6927,20 +6766,18 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>362</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6976,19 +6813,19 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>361</v>
+        <v>296</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7000,30 +6837,30 @@
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>367</v>
+        <v>220</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>368</v>
+        <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7037,28 +6874,28 @@
         <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>370</v>
+        <v>298</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>371</v>
+        <v>299</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>373</v>
+        <v>301</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>374</v>
+        <v>302</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7107,7 +6944,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>369</v>
+        <v>303</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7119,30 +6956,30 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>375</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>376</v>
+        <v>304</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7156,25 +6993,29 @@
         <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>288</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7222,7 +7063,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7234,10 +7075,10 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
@@ -7246,7 +7087,7 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7254,21 +7095,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7280,18 +7121,18 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>293</v>
+        <v>357</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7339,31 +7180,31 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>356</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7371,14 +7212,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7391,25 +7232,25 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>192</v>
+        <v>364</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7458,7 +7299,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7470,19 +7311,19 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -7490,10 +7331,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7504,7 +7345,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>90</v>
@@ -7516,17 +7357,17 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7551,11 +7392,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7573,13 +7416,13 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
@@ -7588,7 +7431,7 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>389</v>
+        <v>275</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>220</v>
@@ -7597,7 +7440,7 @@
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7605,10 +7448,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7631,16 +7474,18 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>288</v>
+        <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>289</v>
+        <v>372</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>290</v>
+        <v>373</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7664,13 +7509,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7688,7 +7533,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>291</v>
+        <v>371</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7700,19 +7545,19 @@
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -7720,21 +7565,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7746,18 +7591,18 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>377</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>293</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7793,54 +7638,54 @@
         <v>81</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>296</v>
+        <v>376</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7851,32 +7696,28 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>298</v>
+        <v>385</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>299</v>
+        <v>386</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7924,13 +7765,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>303</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -7939,16 +7780,16 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>304</v>
+        <v>388</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -7956,10 +7797,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7970,7 +7811,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -7982,16 +7823,20 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8039,25 +7884,25 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>220</v>
+        <v>394</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>81</v>
+        <v>395</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -8071,21 +7916,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8097,17 +7942,15 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>134</v>
+        <v>288</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8144,31 +7987,31 @@
         <v>81</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>220</v>
@@ -8188,21 +8031,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8211,23 +8054,21 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8275,22 +8116,22 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>314</v>
+        <v>220</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
@@ -8299,7 +8140,7 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8307,44 +8148,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>288</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8392,22 +8235,22 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>321</v>
+        <v>132</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
@@ -8416,7 +8259,7 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>322</v>
+        <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8424,10 +8267,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8435,7 +8278,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
@@ -8447,20 +8290,22 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>324</v>
+        <v>400</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>326</v>
+        <v>403</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8485,13 +8330,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8509,10 +8354,10 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>327</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>89</v>
@@ -8524,16 +8369,16 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>328</v>
+        <v>404</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>329</v>
+        <v>406</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8541,10 +8386,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8564,21 +8409,19 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>288</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>331</v>
+        <v>289</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>332</v>
+        <v>290</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>333</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -8626,7 +8469,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8638,10 +8481,10 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>335</v>
+        <v>220</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>81</v>
@@ -8650,7 +8493,7 @@
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8658,21 +8501,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -8681,23 +8524,21 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>338</v>
+        <v>293</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>339</v>
+        <v>294</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
@@ -8733,34 +8574,34 @@
         <v>81</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>342</v>
+        <v>296</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>343</v>
+        <v>220</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -8769,18 +8610,18 @@
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8791,10 +8632,10 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>81</v>
@@ -8803,19 +8644,19 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>347</v>
+        <v>300</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>348</v>
+        <v>301</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>349</v>
+        <v>302</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -8864,13 +8705,13 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>350</v>
+        <v>303</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
@@ -8879,7 +8720,7 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -8888,18 +8729,18 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>352</v>
+        <v>305</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8913,26 +8754,28 @@
         <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>223</v>
+        <v>288</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>403</v>
+        <v>307</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -8981,7 +8824,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>402</v>
+        <v>311</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8996,16 +8839,16 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>228</v>
+        <v>312</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>406</v>
+        <v>313</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9013,10 +8856,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9027,7 +8870,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -9039,19 +8882,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>236</v>
+        <v>415</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9100,13 +8943,13 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
@@ -9115,41 +8958,41 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>237</v>
+        <v>416</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>220</v>
+        <v>417</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>81</v>
@@ -9158,18 +9001,18 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>270</v>
+        <v>421</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9217,13 +9060,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9232,7 +9075,7 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>275</v>
+        <v>425</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>220</v>
@@ -9241,7 +9084,7 @@
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9249,10 +9092,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9272,20 +9115,22 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>109</v>
+        <v>377</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9310,13 +9155,13 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -9334,7 +9179,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9349,16 +9194,16 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>248</v>
+        <v>382</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>220</v>
+        <v>432</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
@@ -9366,10 +9211,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9380,29 +9225,31 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>423</v>
+        <v>331</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9451,22 +9298,22 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>427</v>
+        <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>220</v>
@@ -9475,7 +9322,7 @@
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9483,10 +9330,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9509,13 +9356,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>431</v>
+        <v>288</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>432</v>
+        <v>289</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>433</v>
+        <v>290</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9566,7 +9413,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>430</v>
+        <v>291</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9578,13 +9425,13 @@
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>434</v>
+        <v>220</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
@@ -9598,14 +9445,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9624,20 +9471,18 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>370</v>
+        <v>134</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>436</v>
+        <v>293</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>437</v>
+        <v>294</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -9685,7 +9530,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>296</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9697,13 +9542,13 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9717,42 +9562,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>288</v>
+        <v>134</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>289</v>
+        <v>342</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -9800,22 +9649,22 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>291</v>
+        <v>344</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
@@ -9832,21 +9681,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -9855,19 +9704,19 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>443</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>293</v>
+        <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>294</v>
+        <v>445</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>192</v>
+        <v>446</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9917,31 +9766,31 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>296</v>
+        <v>442</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
@@ -9949,46 +9798,42 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>381</v>
+        <v>449</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10012,13 +9857,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10036,25 +9881,25 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>383</v>
+        <v>448</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>132</v>
+        <v>452</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -10063,2478 +9908,11 @@
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO90" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO90">
+  <autoFilter ref="A1:AO69">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12544,7 +9922,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI89">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
